--- a/datasets/production-like-corpus/corpus/security/SEC-002_数据分类分级标准.xlsx
+++ b/datasets/production-like-corpus/corpus/security/SEC-002_数据分类分级标准.xlsx
@@ -524,7 +524,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -537,7 +537,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：SEC-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
+          <t>文档编号：NT-SECU-MAT-2026-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>官网公开信息；SEC-001：数据分L1/L2/L3/L4</t>
+          <t>官网公开信息；数据分L1/L2/L3/L4</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>员工通讯录</t>
+          <t>员工通讯录；USB使用受信息安全等级约束</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -688,7 +688,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：SEC-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
+          <t>文档编号：NT-SECU-MAT-2026-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>SEC-002：员工通讯录属于L2</t>
+          <t>员工通讯录属于L2</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SEC-003：未公开财务数据属于L3</t>
+          <t>未公开财务数据属于L3</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SEC-004：客户身份证数据属于L3</t>
+          <t>客户身份证数据属于L3</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SEC-005：生产数据库密钥属于L4</t>
+          <t>生产数据库密钥属于L4</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：SEC-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
+          <t>文档编号：NT-SECU-MAT-2026-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -991,7 +991,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：SEC-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
+          <t>文档编号：NT-SECU-MAT-2026-002    版本：V3.1    归口部门：SECURITY    生效日：2026-02-01</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>SEC-006：L3/L4数据要求受控存储和加密</t>
+          <t>L3/L4数据要求受控存储和加密</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>SEC-006：L3/L4数据要求受控存储和加密</t>
+          <t>L3/L4数据要求受控存储和加密</t>
         </is>
       </c>
     </row>
